--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Obj.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Obj.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.252</t>
+    <t xml:space="preserve">EA 23.260</t>
   </si>
   <si>
     <t xml:space="preserve">momiji</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Obj.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Obj.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.260</t>
+    <t xml:space="preserve">EA 23.267</t>
   </si>
   <si>
     <t xml:space="preserve">momiji</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Obj.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Obj.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.267</t>
+    <t xml:space="preserve">EA 23.281</t>
   </si>
   <si>
     <t xml:space="preserve">momiji</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Obj.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Obj.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.281</t>
+    <t xml:space="preserve">EA 23.282 Patch 2</t>
   </si>
   <si>
     <t xml:space="preserve">momiji</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Obj.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Obj.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="597">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -1787,6 +1787,33 @@
   </si>
   <si>
     <t xml:space="preserve">卵</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">장미</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">バラ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">수국</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hydrangea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">アジサイ</t>
   </si>
 </sst>
 </file>
@@ -2015,7 +2042,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H148"/>
+  <dimension ref="A1:H150"/>
   <sheetFormatPr defaultColWidth="8.7578125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="1" style="0" width="16.15"/>
@@ -4527,6 +4554,40 @@
       </c>
       <c r="E148" s="0" t="s">
         <v>587</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="0" t="s">
+        <v>588</v>
+      </c>
+      <c r="B149" s="0" t="s">
+        <v>589</v>
+      </c>
+      <c r="C149" s="0" t="s">
+        <v>590</v>
+      </c>
+      <c r="D149" s="0" t="s">
+        <v>591</v>
+      </c>
+      <c r="E149" s="0" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="0" t="s">
+        <v>593</v>
+      </c>
+      <c r="B150" s="0" t="s">
+        <v>589</v>
+      </c>
+      <c r="C150" s="0" t="s">
+        <v>594</v>
+      </c>
+      <c r="D150" s="0" t="s">
+        <v>595</v>
+      </c>
+      <c r="E150" s="0" t="s">
+        <v>596</v>
       </c>
     </row>
   </sheetData>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Obj.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Obj.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="597">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="606">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -1814,6 +1814,33 @@
   </si>
   <si>
     <t xml:space="preserve">アジサイ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.338 Patch 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">차</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">茶</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고구마</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sweet imo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">サツマイーモ</t>
   </si>
 </sst>
 </file>
@@ -2042,7 +2069,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H150"/>
+  <dimension ref="A1:H152"/>
   <sheetFormatPr defaultColWidth="8.7578125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="1" style="0" width="16.15"/>
@@ -4588,6 +4615,40 @@
       </c>
       <c r="E150" s="0" t="s">
         <v>596</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="0" t="s">
+        <v>597</v>
+      </c>
+      <c r="B151" s="0" t="s">
+        <v>598</v>
+      </c>
+      <c r="C151" s="0" t="s">
+        <v>599</v>
+      </c>
+      <c r="D151" s="0" t="s">
+        <v>600</v>
+      </c>
+      <c r="E151" s="0" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="0" t="s">
+        <v>602</v>
+      </c>
+      <c r="B152" s="0" t="s">
+        <v>598</v>
+      </c>
+      <c r="C152" s="0" t="s">
+        <v>603</v>
+      </c>
+      <c r="D152" s="0" t="s">
+        <v>604</v>
+      </c>
+      <c r="E152" s="0" t="s">
+        <v>605</v>
       </c>
     </row>
   </sheetData>
